--- a/data/lab05/out/people.xlsx
+++ b/data/lab05/out/people.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,6 +469,57 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Moscow</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kazan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SPB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Novosibirsk</t>
         </is>
       </c>
     </row>
